--- a/IPC CA RD Y MEX.xlsx
+++ b/IPC CA RD Y MEX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inegobgt-my.sharepoint.com/personal/laalvarado_ine_gob_gt/Documents/Automatizacion IPC/Agosto 2023/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cycastañeda\OneDrive - ine.gob.gt\Documentos\GitHub\INE_docker_ipc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_E78C8671EE91EF8942AF8A751F897D1AAC7041A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{71F032C7-46B4-490B-A83A-867CF83F7F08}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C3712C7-19D6-428E-9E3C-434B3A58D058}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Guatemala" sheetId="1" r:id="rId1"/>
@@ -22,17 +22,28 @@
     <sheet name="Panamá" sheetId="7" r:id="rId7"/>
     <sheet name="México" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="17">
   <si>
     <t>indice</t>
   </si>
@@ -78,12 +89,18 @@
   <si>
     <t>Diciembre</t>
   </si>
+  <si>
+    <t>octubre</t>
+  </si>
+  <si>
+    <t>noviembre</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,12 +142,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -192,8 +203,10 @@
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -511,10 +524,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -525,9 +538,9 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A2" s="2">
-        <v>138.97999999999999</v>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2">
+        <v>79.72</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -536,9 +549,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A3" s="2">
-        <v>139.16999999999999</v>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>79.83</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -547,9 +560,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A4" s="2">
-        <v>139.11000000000001</v>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>79.8</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -558,9 +571,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A5" s="2">
-        <v>139.94999999999999</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>80.27</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -569,9 +582,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A6" s="2">
-        <v>140.32</v>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>80.489999999999995</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -580,9 +593,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" s="2">
-        <v>141.47999999999999</v>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>81.150000000000006</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -591,9 +604,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A8" s="2">
-        <v>141.4</v>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>81.11</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -602,9 +615,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A9" s="2">
-        <v>140.18</v>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>80.41</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
@@ -613,9 +626,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A10" s="2">
-        <v>139.36000000000001</v>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>79.94</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
@@ -624,9 +637,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A11" s="2">
-        <v>140.33000000000001</v>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>80.5</v>
       </c>
       <c r="B11" t="s">
         <v>12</v>
@@ -635,9 +648,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A12" s="2">
-        <v>140.94999999999999</v>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>80.849999999999994</v>
       </c>
       <c r="B12" t="s">
         <v>13</v>
@@ -646,9 +659,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A13" s="2">
-        <v>141.80000000000001</v>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>81.34</v>
       </c>
       <c r="B13" t="s">
         <v>14</v>
@@ -657,9 +670,9 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A14" s="2">
-        <v>141.46</v>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>81.14</v>
       </c>
       <c r="B14" t="s">
         <v>3</v>
@@ -668,9 +681,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A15" s="2">
-        <v>140.88999999999999</v>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>80.81</v>
       </c>
       <c r="B15" t="s">
         <v>4</v>
@@ -679,9 +692,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="2">
-        <v>141.57</v>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>81.2</v>
       </c>
       <c r="B16" t="s">
         <v>5</v>
@@ -690,9 +703,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="2">
-        <v>142.58000000000001</v>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>81.78</v>
       </c>
       <c r="B17" t="s">
         <v>6</v>
@@ -701,9 +714,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="2">
-        <v>142.85</v>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>81.94</v>
       </c>
       <c r="B18" t="s">
         <v>7</v>
@@ -712,9 +725,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="2">
-        <v>144.86000000000001</v>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>83.09</v>
       </c>
       <c r="B19" t="s">
         <v>8</v>
@@ -723,9 +736,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
-        <v>145.47</v>
+        <v>83.44</v>
       </c>
       <c r="B20" t="s">
         <v>9</v>
@@ -734,9 +747,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
-        <v>146.05000000000001</v>
+        <v>83.77</v>
       </c>
       <c r="B21" t="s">
         <v>10</v>
@@ -745,9 +758,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
-        <v>146.28</v>
+        <v>83.9</v>
       </c>
       <c r="B22" t="s">
         <v>11</v>
@@ -756,9 +769,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
-        <v>147.83000000000001</v>
+        <v>84.8</v>
       </c>
       <c r="B23" t="s">
         <v>12</v>
@@ -767,9 +780,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
-        <v>148.65</v>
+        <v>85.26</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -778,9 +791,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
-        <v>148.63999999999999</v>
+        <v>85.26</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -789,9 +802,9 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
-        <v>148.87</v>
+        <v>85.4</v>
       </c>
       <c r="B26" t="s">
         <v>3</v>
@@ -800,9 +813,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
-        <v>149.34</v>
+        <v>85.66</v>
       </c>
       <c r="B27" t="s">
         <v>4</v>
@@ -811,9 +824,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
-        <v>149.84</v>
+        <v>85.95</v>
       </c>
       <c r="B28" t="s">
         <v>5</v>
@@ -822,9 +835,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
-        <v>150</v>
+        <v>86.04</v>
       </c>
       <c r="B29" t="s">
         <v>6</v>
@@ -833,9 +846,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
-        <v>150.24</v>
+        <v>86.18</v>
       </c>
       <c r="B30" t="s">
         <v>7</v>
@@ -844,9 +857,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
-        <v>150.52000000000001</v>
+        <v>86.34</v>
       </c>
       <c r="B31" t="s">
         <v>8</v>
@@ -855,9 +868,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
-        <v>151.02000000000001</v>
+        <v>86.62</v>
       </c>
       <c r="B32" t="s">
         <v>9</v>
@@ -866,9 +879,9 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
-        <v>151.33000000000001</v>
+        <v>86.8</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -879,7 +892,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>151.65</v>
+        <v>86.99</v>
       </c>
       <c r="B34" t="s">
         <v>11</v>
@@ -890,7 +903,7 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>152.19999999999999</v>
+        <v>87.3</v>
       </c>
       <c r="B35" t="s">
         <v>12</v>
@@ -901,7 +914,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
-        <v>152.94</v>
+        <v>87.73</v>
       </c>
       <c r="B36" t="s">
         <v>13</v>
@@ -912,7 +925,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
-        <v>153.19999999999999</v>
+        <v>87.87</v>
       </c>
       <c r="B37" t="s">
         <v>14</v>
@@ -923,7 +936,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
-        <v>153.13999999999999</v>
+        <v>87.84</v>
       </c>
       <c r="B38" t="s">
         <v>3</v>
@@ -934,7 +947,7 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
-        <v>153.79</v>
+        <v>88.21</v>
       </c>
       <c r="B39" t="s">
         <v>4</v>
@@ -945,7 +958,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
-        <v>156.09</v>
+        <v>89.531949065045296</v>
       </c>
       <c r="B40" t="s">
         <v>5</v>
@@ -956,7 +969,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
-        <v>156.93</v>
+        <v>90.01</v>
       </c>
       <c r="B41" t="s">
         <v>6</v>
@@ -967,7 +980,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
-        <v>158.97999999999999</v>
+        <v>91.19</v>
       </c>
       <c r="B42" t="s">
         <v>7</v>
@@ -978,7 +991,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
-        <v>161.88999999999999</v>
+        <v>92.86</v>
       </c>
       <c r="B43" t="s">
         <v>8</v>
@@ -989,7 +1002,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
-        <v>163.63999999999999</v>
+        <v>93.86</v>
       </c>
       <c r="B44" t="s">
         <v>9</v>
@@ -1000,7 +1013,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
-        <v>164.76</v>
+        <v>94.5</v>
       </c>
       <c r="B45" t="s">
         <v>10</v>
@@ -1011,7 +1024,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
-        <v>165.35</v>
+        <v>94.84</v>
       </c>
       <c r="B46" t="s">
         <v>11</v>
@@ -1022,7 +1035,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
-        <v>166.97</v>
+        <v>95.77</v>
       </c>
       <c r="B47" t="s">
         <v>12</v>
@@ -1033,7 +1046,7 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
-        <v>166.96</v>
+        <v>95.77</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -1044,7 +1057,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
-        <v>167.35</v>
+        <v>96</v>
       </c>
       <c r="B49" t="s">
         <v>14</v>
@@ -1055,7 +1068,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>167.98</v>
+        <v>95.225214991168997</v>
       </c>
       <c r="B50" t="s">
         <v>3</v>
@@ -1066,7 +1079,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>169.05</v>
+        <v>95.831781130236493</v>
       </c>
       <c r="B51" t="s">
         <v>4</v>
@@ -1077,7 +1090,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
-        <v>169.69</v>
+        <v>96.194587045192705</v>
       </c>
       <c r="B52" s="9" t="s">
         <v>5</v>
@@ -1088,7 +1101,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
-        <v>169.98</v>
+        <v>96.3589834754072</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
@@ -1098,8 +1111,8 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10">
-        <v>169.37</v>
+      <c r="A54" s="5">
+        <v>96.013184087714606</v>
       </c>
       <c r="B54" t="s">
         <v>7</v>
@@ -1110,7 +1123,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
-        <v>169.87</v>
+        <v>96.2966262087741</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
@@ -1120,14 +1133,278 @@
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>171.06</v>
+      <c r="A56" s="2">
+        <v>96.971218456895897</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
       </c>
       <c r="C56">
         <v>2023</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>97.577784595963294</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>98.127662310818906</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2">
+        <v>99.369138801059705</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
+        <v>98.717221922622798</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2">
+        <v>98.830598771046596</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>98.856695978958101</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>98.994617044461094</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>99.300106378486305</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>99.594133215471601</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>99.622504993395694</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>99.781554698869499</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>100.63825983786801</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>100.575543385682</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>100.196314506457</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>100.52599686060999</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>100.355601844182</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>100.513540673813</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>101.02</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>100.77</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>100.862479384954</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>101.058686802872</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>101.306106231022</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>101.56274012722299</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>101.81</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
       </c>
     </row>
   </sheetData>
@@ -1139,10 +1416,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:I80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1153,7 +1430,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>112.24</v>
       </c>
@@ -1164,7 +1441,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>112.44</v>
       </c>
@@ -1175,7 +1452,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>112.69</v>
       </c>
@@ -1186,7 +1463,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>112.87</v>
       </c>
@@ -1197,7 +1474,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>113.01</v>
       </c>
@@ -1208,7 +1485,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>112.85</v>
       </c>
@@ -1219,7 +1496,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>112.56</v>
       </c>
@@ -1230,7 +1507,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>112.16</v>
       </c>
@@ -1241,7 +1518,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>111.99</v>
       </c>
@@ -1252,7 +1529,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>112.04</v>
       </c>
@@ -1263,7 +1540,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>112.17</v>
       </c>
@@ -1274,7 +1551,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>112.29</v>
       </c>
@@ -1285,7 +1562,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>112.15</v>
       </c>
@@ -1296,7 +1573,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>112</v>
       </c>
@@ -1307,7 +1584,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>112.09</v>
       </c>
@@ -1318,7 +1595,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>111.69</v>
       </c>
@@ -1329,7 +1606,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>111.94</v>
       </c>
@@ -1340,7 +1617,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>112.59</v>
       </c>
@@ -1351,7 +1628,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>112.49</v>
       </c>
@@ -1362,7 +1639,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>111.82</v>
       </c>
@@ -1373,7 +1650,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>111.56</v>
       </c>
@@ -1384,7 +1661,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>111.81</v>
       </c>
@@ -1395,7 +1672,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>111.98</v>
       </c>
@@ -1406,7 +1683,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>112.2</v>
       </c>
@@ -1417,7 +1694,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>112.49</v>
       </c>
@@ -1428,7 +1705,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>113.19</v>
       </c>
@@ -1439,7 +1716,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>114.08</v>
       </c>
@@ -1450,7 +1727,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>114.81</v>
       </c>
@@ -1461,7 +1738,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>114.84</v>
       </c>
@@ -1472,7 +1749,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>115.51</v>
       </c>
@@ -1483,7 +1760,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>116.36</v>
       </c>
@@ -1494,7 +1771,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>116.63</v>
       </c>
@@ -1505,7 +1782,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>117.1</v>
       </c>
@@ -1516,7 +1793,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>117.95</v>
       </c>
@@ -1527,7 +1804,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>118.92</v>
       </c>
@@ -1538,7 +1815,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>119.06</v>
       </c>
@@ -1549,7 +1826,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>119.79</v>
       </c>
@@ -1560,7 +1837,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>120.73</v>
       </c>
@@ -1571,7 +1848,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>121.71</v>
       </c>
@@ -1582,7 +1859,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>122.32</v>
       </c>
@@ -1593,7 +1870,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>123.43</v>
       </c>
@@ -1604,7 +1881,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>124.47</v>
       </c>
@@ -1615,7 +1892,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>124.99</v>
       </c>
@@ -1626,7 +1903,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>125.56</v>
       </c>
@@ -1637,7 +1914,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>125.87</v>
       </c>
@@ -1648,7 +1925,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>126.76</v>
       </c>
@@ -1659,7 +1936,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <v>127.63</v>
       </c>
@@ -1670,7 +1947,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>127.77</v>
       </c>
@@ -1681,7 +1958,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <v>128.21</v>
       </c>
@@ -1692,7 +1969,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>128.97</v>
       </c>
@@ -1703,7 +1980,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>129.08000000000001</v>
       </c>
@@ -1714,7 +1991,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>128.97</v>
       </c>
@@ -1725,7 +2002,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>128.88</v>
       </c>
@@ -1736,7 +2013,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>129.18</v>
       </c>
@@ -1747,7 +2024,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>129.16999999999999</v>
       </c>
@@ -1758,20 +2035,286 @@
         <v>2023</v>
       </c>
     </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>129.44</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>129.66999999999999</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
+        <v>130.13999999999999</v>
+      </c>
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A60" s="10">
+        <v>130.32</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
+        <v>129.34</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+      <c r="I61" s="2"/>
+    </row>
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
+        <v>129.76</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>130</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
+        <v>130.08000000000001</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>130.44999999999999</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10">
+        <v>130.71</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="10">
+        <v>131.09</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
+        <v>131.47</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
+        <v>130.96</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
+        <v>130.41999999999999</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10">
+        <v>130.04</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="10">
+        <v>129.93</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
+        <v>129.71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="10">
+        <v>130.16</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
+        <v>130.08000000000001</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="10">
+        <v>130.26</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>130.30000000000001</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>130.44</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>130.86000000000001</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="15">
+        <v>131.29</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
@@ -1782,7 +2325,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>323.3</v>
       </c>
@@ -1793,7 +2336,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>325.8</v>
       </c>
@@ -1804,7 +2347,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>327.10000000000002</v>
       </c>
@@ -1815,7 +2358,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>330.1</v>
       </c>
@@ -1826,7 +2369,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>331.3</v>
       </c>
@@ -1837,7 +2380,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>331.6</v>
       </c>
@@ -1848,7 +2391,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>332.5</v>
       </c>
@@ -1859,7 +2402,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>332.7</v>
       </c>
@@ -1870,7 +2413,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>333.2</v>
       </c>
@@ -1881,7 +2424,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>334</v>
       </c>
@@ -1892,7 +2435,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>335</v>
       </c>
@@ -1903,7 +2446,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>336.4</v>
       </c>
@@ -1914,7 +2457,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>337.2</v>
       </c>
@@ -1925,7 +2468,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>338.8</v>
       </c>
@@ -1936,7 +2479,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>339.8</v>
       </c>
@@ -1947,7 +2490,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>341.1</v>
       </c>
@@ -1958,7 +2501,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>338.9</v>
       </c>
@@ -1969,7 +2512,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>340.4</v>
       </c>
@@ -1980,7 +2523,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>342.8</v>
       </c>
@@ -1991,7 +2534,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>343.4</v>
       </c>
@@ -2002,7 +2545,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>344.5</v>
       </c>
@@ -2013,7 +2556,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>346.2</v>
       </c>
@@ -2024,7 +2567,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>347.8</v>
       </c>
@@ -2035,7 +2578,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>349.9</v>
       </c>
@@ -2046,7 +2589,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>351.3</v>
       </c>
@@ -2057,7 +2600,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>351.9</v>
       </c>
@@ -2068,7 +2611,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>353.2</v>
       </c>
@@ -2079,7 +2622,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>354.6</v>
       </c>
@@ -2090,7 +2633,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>355.3</v>
       </c>
@@ -2101,7 +2644,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>356.3</v>
       </c>
@@ -2112,7 +2655,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>357.4</v>
       </c>
@@ -2123,7 +2666,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>358.8</v>
       </c>
@@ -2134,7 +2677,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>360.4</v>
       </c>
@@ -2145,7 +2688,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>362.3</v>
       </c>
@@ -2156,7 +2699,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>365</v>
       </c>
@@ -2167,7 +2710,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>368.5</v>
       </c>
@@ -2178,7 +2721,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>373</v>
       </c>
@@ -2189,7 +2732,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>374.3</v>
       </c>
@@ -2200,7 +2743,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>377.8</v>
       </c>
@@ -2211,7 +2754,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>384.2</v>
       </c>
@@ -2222,7 +2765,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>387.6</v>
       </c>
@@ -2233,7 +2776,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>392.7</v>
       </c>
@@ -2244,7 +2787,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>396.2</v>
       </c>
@@ -2255,7 +2798,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>396.1</v>
       </c>
@@ -2266,7 +2809,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>396.6</v>
       </c>
@@ -2277,7 +2820,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
         <v>399.2</v>
       </c>
@@ -2288,7 +2831,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
         <v>403.1</v>
       </c>
@@ -2299,7 +2842,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="11">
         <v>404.6</v>
       </c>
@@ -2310,7 +2853,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="11">
         <v>406.3</v>
       </c>
@@ -2321,7 +2864,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="11">
         <v>411</v>
       </c>
@@ -2388,19 +2931,281 @@
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" s="5"/>
+      <c r="A57" s="5">
+        <v>418.7</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="5">
+        <v>420.9</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>422.5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>15</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>423.4</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>425.6</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>426.6</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>429.5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>431.6</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>432.8</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>433.5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>434.9</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>437.7</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>439.6</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>439.8</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>439.6</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>440.1</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>442.1</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>444.8</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>449.9</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>451</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>451.8</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>453.2</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>455.2</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="15">
+        <v>457</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2411,7 +3216,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>218.6</v>
       </c>
@@ -2422,7 +3227,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>219.2</v>
       </c>
@@ -2433,7 +3238,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>223.19</v>
       </c>
@@ -2444,7 +3249,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>225.34</v>
       </c>
@@ -2455,7 +3260,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>227.06</v>
       </c>
@@ -2466,7 +3271,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>227.26</v>
       </c>
@@ -2477,7 +3282,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>228.05</v>
       </c>
@@ -2488,7 +3293,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>227.98</v>
       </c>
@@ -2499,7 +3304,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>227.67</v>
       </c>
@@ -2510,7 +3315,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>228.44</v>
       </c>
@@ -2521,7 +3326,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>230.24</v>
       </c>
@@ -2532,7 +3337,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>232.59</v>
       </c>
@@ -2543,7 +3348,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>232.63</v>
       </c>
@@ -2554,7 +3359,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>233.26</v>
       </c>
@@ -2565,7 +3370,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>233.05</v>
       </c>
@@ -2576,7 +3381,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>232.65</v>
       </c>
@@ -2587,7 +3392,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>233.62</v>
       </c>
@@ -2598,7 +3403,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>235.49</v>
       </c>
@@ -2609,7 +3414,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>235.91</v>
       </c>
@@ -2620,7 +3425,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>234.53</v>
       </c>
@@ -2631,7 +3436,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>234.06</v>
       </c>
@@ -2642,7 +3447,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>234.58</v>
       </c>
@@ -2653,7 +3458,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>236.33</v>
       </c>
@@ -2664,7 +3469,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>239.4</v>
       </c>
@@ -2675,7 +3480,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>240.03</v>
       </c>
@@ -2686,7 +3491,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>242.06</v>
       </c>
@@ -2697,7 +3502,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>242.63</v>
       </c>
@@ -2708,7 +3513,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>242.89</v>
       </c>
@@ -2719,7 +3524,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>243.01</v>
       </c>
@@ -2730,7 +3535,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>244.77</v>
       </c>
@@ -2741,7 +3546,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>245.62</v>
       </c>
@@ -2752,7 +3557,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>246.21</v>
       </c>
@@ -2763,7 +3568,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>247.77</v>
       </c>
@@ -2774,7 +3579,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>249.62</v>
       </c>
@@ -2785,7 +3590,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>253.1</v>
       </c>
@@ -2796,7 +3601,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>256.66000000000003</v>
       </c>
@@ -2807,7 +3612,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>258.47000000000003</v>
       </c>
@@ -2818,7 +3623,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>260.33</v>
       </c>
@@ -2829,7 +3634,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>263.83999999999997</v>
       </c>
@@ -2840,7 +3645,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>267.05</v>
       </c>
@@ -2851,7 +3656,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>268.79000000000002</v>
       </c>
@@ -2862,7 +3667,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>270.14999999999998</v>
       </c>
@@ -2873,7 +3678,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>273.76</v>
       </c>
@@ -2884,7 +3689,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>276.12</v>
       </c>
@@ -2895,7 +3700,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>276.31</v>
       </c>
@@ -2906,7 +3711,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>280</v>
       </c>
@@ -2917,7 +3722,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>281.89999999999998</v>
       </c>
@@ -2941,7 +3746,7 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
-        <v>286.7</v>
+        <v>286.70291099999997</v>
       </c>
       <c r="B50" t="s">
         <v>3</v>
@@ -2952,7 +3757,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>289.79000000000002</v>
+        <v>289.788027</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>4</v>
@@ -2963,7 +3768,7 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>291.2</v>
+        <v>291.24409399999996</v>
       </c>
       <c r="B52" t="s">
         <v>5</v>
@@ -2974,7 +3779,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
-        <v>292.52</v>
+        <v>292.51535999999999</v>
       </c>
       <c r="B53" t="s">
         <v>6</v>
@@ -2984,8 +3789,8 @@
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" s="10">
-        <v>294.24</v>
+      <c r="A54" s="5">
+        <v>294.24477200000001</v>
       </c>
       <c r="B54" t="s">
         <v>7</v>
@@ -2995,8 +3800,8 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>296.82</v>
+      <c r="A55" s="2">
+        <v>296.82079699999997</v>
       </c>
       <c r="B55" t="s">
         <v>8</v>
@@ -3007,7 +3812,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
-        <v>296.10000000000002</v>
+        <v>296.134793</v>
       </c>
       <c r="B56" t="s">
         <v>9</v>
@@ -3016,17 +3821,282 @@
         <v>2023</v>
       </c>
     </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>296.71436699999998</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>296.12500999999997</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>296.78847500000001</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>297.80682200000001</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>302.46986599999997</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>303.30210699999998</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2">
+        <v>304.08391799999998</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>307.08193899999998</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>308.41022099999998</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>310.26851799999997</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>311.12126899999998</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>311.61611899999997</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>310.135582</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>307.56744800000001</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>307.49273399999998</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
+        <v>308.872454</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>311.04830499999997</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>311.57890099999997</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>314.57817999999997</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>313.63932199999999</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2">
+        <v>313.74</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>314.27797199999998</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>313.887584</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="7">
+        <v>313.62</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C58"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3037,7 +4107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>97.679211870000003</v>
       </c>
@@ -3048,7 +4118,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>97.759031789999995</v>
       </c>
@@ -3059,7 +4129,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>97.617418020000002</v>
       </c>
@@ -3070,7 +4140,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>98.165424299999998</v>
       </c>
@@ -3081,7 +4151,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>98.298055500000004</v>
       </c>
@@ -3092,7 +4162,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>98.568195180000004</v>
       </c>
@@ -3103,7 +4173,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>99.291642809999999</v>
       </c>
@@ -3114,7 +4184,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>99.193890580000001</v>
       </c>
@@ -3125,7 +4195,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>99.097494049999995</v>
       </c>
@@ -3136,7 +4206,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>99.024797930000005</v>
       </c>
@@ -3147,7 +4217,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>99.231689320000001</v>
       </c>
@@ -3158,7 +4228,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>99.115445679999993</v>
       </c>
@@ -3169,7 +4239,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>99.225243599999999</v>
       </c>
@@ -3180,7 +4250,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>99.508993009999998</v>
       </c>
@@ -3191,7 +4261,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>99.478912469999997</v>
       </c>
@@ -3202,7 +4272,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>99.040237869999999</v>
       </c>
@@ -3213,7 +4283,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>98.896445709999995</v>
       </c>
@@ -3224,7 +4294,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>98.875348310000007</v>
       </c>
@@ -3235,7 +4305,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>99.127692339999996</v>
       </c>
@@ -3246,7 +4316,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>99.123686579999998</v>
       </c>
@@ -3257,7 +4327,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>99.393758820000002</v>
       </c>
@@ -3268,7 +4338,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>99.472841919999993</v>
       </c>
@@ -3279,7 +4349,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>99.474323560000002</v>
       </c>
@@ -3290,7 +4360,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>100</v>
       </c>
@@ -3301,7 +4371,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>100.18</v>
       </c>
@@ -3312,7 +4382,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>99.921244529999996</v>
       </c>
@@ -3323,7 +4393,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>99.949181179999997</v>
       </c>
@@ -3334,7 +4404,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>100.2384619</v>
       </c>
@@ -3345,7 +4415,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>100.22344409999999</v>
       </c>
@@ -3356,7 +4426,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>100.7619232</v>
       </c>
@@ -3367,7 +4437,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>100.5549128</v>
       </c>
@@ -3378,7 +4448,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>100.8332302</v>
       </c>
@@ -3389,7 +4459,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>101.4674681</v>
       </c>
@@ -3400,7 +4470,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>101.96356230000001</v>
       </c>
@@ -3411,7 +4481,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>102.80237959999999</v>
       </c>
@@ -3422,7 +4492,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>103.2989079</v>
       </c>
@@ -3433,7 +4503,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>103.6812099</v>
       </c>
@@ -3444,7 +4514,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>104.8147022</v>
       </c>
@@ -3455,7 +4525,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>105.7394122</v>
       </c>
@@ -3466,7 +4536,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>107.40707740000001</v>
       </c>
@@ -3477,7 +4547,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>108.97</v>
       </c>
@@ -3488,7 +4558,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>110.89</v>
       </c>
@@ -3499,7 +4569,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>112.1</v>
       </c>
@@ -3510,7 +4580,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>113.06</v>
       </c>
@@ -3521,7 +4591,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>111.98</v>
       </c>
@@ -3642,10 +4712,272 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A58" s="14"/>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>109.35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>109.48</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
+        <v>109.71</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="10">
+        <v>109.45</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
+        <v>109.46</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
+        <v>109.52</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
+        <v>109.41</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>109.1</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>109.46</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="10">
+        <v>109.55</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>109.7</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
+        <v>109.57</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="10">
+        <v>109.69</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
+        <v>109.33</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10">
+        <v>108.85</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>109.35</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
+        <v>110.39</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="10">
+        <v>110.78</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="10">
+        <v>110.77</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="10">
+        <v>110.42</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="10">
+        <v>109.87</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="10">
+        <v>109.42</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="10">
+        <v>109.46</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="15">
+        <v>108.9</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -3653,10 +4985,10 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3667,7 +4999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>95.250891820000007</v>
       </c>
@@ -3678,7 +5010,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>95.604163560000003</v>
       </c>
@@ -3689,7 +5021,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>96.229748920000006</v>
       </c>
@@ -3700,7 +5032,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>96.737577040000005</v>
       </c>
@@ -3711,7 +5043,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>96.708137730000004</v>
       </c>
@@ -3722,7 +5054,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>96.53150187</v>
       </c>
@@ -3733,7 +5065,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>96.980451360000004</v>
       </c>
@@ -3744,7 +5076,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>97.311643619999998</v>
       </c>
@@ -3755,7 +5087,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>97.679635009999998</v>
       </c>
@@ -3766,7 +5098,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>98.334659680000001</v>
       </c>
@@ -3777,7 +5109,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>98.702651079999995</v>
       </c>
@@ -3788,7 +5120,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>98.901366429999996</v>
       </c>
@@ -3799,7 +5131,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>99.225198849999998</v>
       </c>
@@ -3810,7 +5142,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>99.100081779999996</v>
       </c>
@@ -3821,7 +5153,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>98.584893829999999</v>
       </c>
@@ -3832,7 +5164,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>97.775312769999999</v>
       </c>
@@ -3843,7 +5175,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>97.664915350000001</v>
       </c>
@@ -3854,7 +5186,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>99.328236439999998</v>
       </c>
@@ -3865,7 +5197,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>101.1976327</v>
       </c>
@@ -3876,7 +5208,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>101.9851343</v>
       </c>
@@ -3887,7 +5219,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>102.596</v>
       </c>
@@ -3898,7 +5230,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>103.276</v>
       </c>
@@ -3909,7 +5241,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>103.893</v>
       </c>
@@ -3920,7 +5252,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>104.39400000000001</v>
       </c>
@@ -3931,7 +5263,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>105.404</v>
       </c>
@@ -3942,7 +5274,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>106.124</v>
       </c>
@@ -3953,7 +5285,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>106.764</v>
       </c>
@@ -3964,7 +5296,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>107.206</v>
       </c>
@@ -3975,7 +5307,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>107.901</v>
       </c>
@@ -3986,7 +5318,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>108.58499999999999</v>
       </c>
@@ -3997,7 +5329,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>109.16800000000001</v>
       </c>
@@ -4008,7 +5340,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>110.039</v>
       </c>
@@ -4019,7 +5351,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>110.535</v>
       </c>
@@ -4030,7 +5362,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>111.244</v>
       </c>
@@ -4041,7 +5373,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>112.446</v>
       </c>
@@ -4052,7 +5384,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>113.26300000000001</v>
       </c>
@@ -4063,7 +5395,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>114.602</v>
       </c>
@@ -4074,7 +5406,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>115.658</v>
       </c>
@@ -4085,7 +5417,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>116.431</v>
       </c>
@@ -4096,7 +5428,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>117.544</v>
       </c>
@@ -4107,7 +5439,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>118.122</v>
       </c>
@@ -4118,7 +5450,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>118.877</v>
       </c>
@@ -4129,7 +5461,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>119.468</v>
       </c>
@@ -4140,7 +5472,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>119.718</v>
       </c>
@@ -4151,7 +5483,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>120.07</v>
       </c>
@@ -4251,7 +5583,7 @@
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" s="15">
+      <c r="A55" s="14">
         <v>123.63</v>
       </c>
       <c r="B55" t="s">
@@ -4272,7 +5604,272 @@
         <v>2023</v>
       </c>
     </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>124.83</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58">
+        <v>125.37</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="10">
+        <v>125.64</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="10">
+        <v>125.81</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="10">
+        <v>126.49</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="10">
+        <v>126.98</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="10">
+        <v>127.09</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="10">
+        <v>127.47</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="10">
+        <v>127.35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>127.3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="10">
+        <v>127.91</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="10">
+        <v>128.58000000000001</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>129.1</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="10">
+        <v>129.49</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="10">
+        <v>129.61000000000001</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="10">
+        <v>129.81</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="10">
+        <v>130.72</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>131.2004</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>131.62440000000001</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>132.03729999999999</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77">
+        <v>132.07</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
+        <v>132.1823</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2">
+        <v>132.45519999999999</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="15">
+        <v>132.94999999999999</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -4280,10 +5877,10 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4294,7 +5891,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>104.3818788</v>
       </c>
@@ -4305,7 +5902,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>104.47547969999999</v>
       </c>
@@ -4316,7 +5913,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>104.9075837</v>
       </c>
@@ -4327,7 +5924,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>105.20208649999999</v>
       </c>
@@ -4338,7 +5935,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>105.29618739999999</v>
       </c>
@@ -4349,7 +5946,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>104.9474841</v>
       </c>
@@ -4360,7 +5957,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>105.17908629999999</v>
       </c>
@@ -4371,7 +5968,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>104.8893836</v>
       </c>
@@ -4382,7 +5979,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>104.8395831</v>
       </c>
@@ -4393,7 +5990,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>104.7846826</v>
       </c>
@@ -4404,7 +6001,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>104.7690824</v>
       </c>
@@ -4415,7 +6012,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>104.6009808</v>
       </c>
@@ -4426,7 +6023,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>104.7532823</v>
       </c>
@@ -4437,7 +6034,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>104.49057980000001</v>
       </c>
@@ -4448,7 +6045,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>104.0266755</v>
       </c>
@@ -4459,7 +6056,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>102.7049631</v>
       </c>
@@ -4470,7 +6067,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>102.69636300000001</v>
       </c>
@@ -4481,7 +6078,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>103.23016800000001</v>
       </c>
@@ -4492,7 +6089,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>102.8125641</v>
       </c>
@@ -4503,7 +6100,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>102.8296642</v>
       </c>
@@ -4514,7 +6111,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>102.8910648</v>
       </c>
@@ -4525,7 +6122,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>102.74256339999999</v>
       </c>
@@ -4536,7 +6133,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>102.63536240000001</v>
       </c>
@@ -4547,7 +6144,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>102.9521654</v>
       </c>
@@ -4558,7 +6155,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>104.0266755</v>
       </c>
@@ -4569,7 +6166,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>103.8786741</v>
       </c>
@@ -4580,7 +6177,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>104.3266783</v>
       </c>
@@ -4591,7 +6188,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>104.4563795</v>
       </c>
@@ -4602,7 +6199,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>104.6722815</v>
       </c>
@@ -4613,7 +6210,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>104.8612833</v>
       </c>
@@ -4624,7 +6221,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>105.251687</v>
       </c>
@@ -4635,7 +6232,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>105.2900873</v>
       </c>
@@ -4646,7 +6243,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>105.44888880000001</v>
       </c>
@@ -4657,7 +6254,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>105.7662918</v>
       </c>
@@ -4668,7 +6265,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>106.0843948</v>
       </c>
@@ -4679,7 +6276,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>105.65399069999999</v>
       </c>
@@ -4690,7 +6287,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>105.98759389999999</v>
       </c>
@@ -4701,7 +6298,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>106.7203007</v>
       </c>
@@ -4712,7 +6309,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>107.64890939999999</v>
       </c>
@@ -4723,7 +6320,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>108.2695152</v>
       </c>
@@ -4734,7 +6331,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>109.08952290000001</v>
       </c>
@@ -4745,7 +6342,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>110.3</v>
       </c>
@@ -4756,7 +6353,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>108.9</v>
       </c>
@@ -4767,7 +6364,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>107.5</v>
       </c>
@@ -4778,7 +6375,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>107.5</v>
       </c>
@@ -4789,7 +6386,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="4">
         <v>107.5</v>
       </c>
@@ -4800,7 +6397,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="4">
         <v>107.7</v>
       </c>
@@ -4899,17 +6496,283 @@
         <v>2023</v>
       </c>
     </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>109.8</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>109.8</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>109.8</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>109.9</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="5">
+        <v>110.2</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>110.6</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>111</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>111.1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>110.9</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>110.6</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>110.4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+      <c r="F68" s="2"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>110.2</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>109.7</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>109.45</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>109.51</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>109.7</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="5">
+        <v>110</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="5">
+        <v>110.41</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="5">
+        <v>110.5</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>110.3</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>110.2</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="10">
+        <v>110.12</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="15">
+        <v>110.05</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4920,7 +6783,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>103.108</v>
       </c>
@@ -4931,7 +6794,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>103.07899999999999</v>
       </c>
@@ -4942,7 +6805,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>103.476</v>
       </c>
@@ -4953,7 +6816,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>103.53100000000001</v>
       </c>
@@ -4964,7 +6827,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>103.233</v>
       </c>
@@ -4975,7 +6838,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>103.29900000000001</v>
       </c>
@@ -4987,7 +6850,7 @@
       </c>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <v>103.687</v>
       </c>
@@ -4998,7 +6861,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>103.67</v>
       </c>
@@ -5009,7 +6872,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>103.94199999999999</v>
       </c>
@@ -5020,7 +6883,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>104.503</v>
       </c>
@@ -5031,7 +6894,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>105.346</v>
       </c>
@@ -5042,7 +6905,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>105.934</v>
       </c>
@@ -5053,7 +6916,7 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <v>106.447</v>
       </c>
@@ -5064,7 +6927,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>106.889</v>
       </c>
@@ -5075,7 +6938,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>106.83799999999999</v>
       </c>
@@ -5086,7 +6949,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>105.755</v>
       </c>
@@ -5097,7 +6960,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>106.16200000000001</v>
       </c>
@@ -5108,7 +6971,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>106.74299999999999</v>
       </c>
@@ -5119,7 +6982,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <v>107.444</v>
       </c>
@@ -5130,7 +6993,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>107.867</v>
       </c>
@@ -5141,7 +7004,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>108.114</v>
       </c>
@@ -5152,7 +7015,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>108.774</v>
       </c>
@@ -5163,7 +7026,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>108.85599999999999</v>
       </c>
@@ -5174,7 +7037,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>109.271</v>
       </c>
@@ -5185,7 +7048,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>110.21</v>
       </c>
@@ -5196,7 +7059,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>110.907</v>
       </c>
@@ -5207,7 +7070,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <v>111.824</v>
       </c>
@@ -5218,7 +7081,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>112.19</v>
       </c>
@@ -5229,7 +7092,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <v>112.419</v>
       </c>
@@ -5240,7 +7103,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>113.018</v>
       </c>
@@ -5251,7 +7114,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <v>113.682</v>
       </c>
@@ -5262,7 +7125,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>113.899</v>
       </c>
@@ -5273,7 +7136,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <v>114.601</v>
       </c>
@@ -5284,7 +7147,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>115.56100000000001</v>
       </c>
@@ -5295,7 +7158,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <v>116.884</v>
       </c>
@@ -5306,7 +7169,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>117.30800000000001</v>
       </c>
@@ -5317,7 +7180,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <v>118.002</v>
       </c>
@@ -5328,7 +7191,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>118.98099999999999</v>
       </c>
@@ -5339,7 +7202,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <v>120.15900000000001</v>
       </c>
@@ -5350,7 +7213,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>120.809</v>
       </c>
@@ -5361,7 +7224,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <v>121.02200000000001</v>
       </c>
@@ -5372,7 +7235,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>122.044</v>
       </c>
@@ -5383,7 +7246,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <v>122.95</v>
       </c>
@@ -5394,7 +7257,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>123.8</v>
       </c>
@@ -5405,7 +7268,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <v>124.57</v>
       </c>
@@ -5416,7 +7279,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
         <v>125.3</v>
       </c>
@@ -5427,7 +7290,7 @@
         <v>2022</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
         <v>126</v>
       </c>
@@ -5526,7 +7389,272 @@
         <v>2023</v>
       </c>
     </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2">
+        <v>129.5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>10</v>
+      </c>
+      <c r="C57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
+        <v>130.1</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="5">
+        <v>130.6</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="5">
+        <v>131.4</v>
+      </c>
+      <c r="B60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C60">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="5">
+        <v>132.4</v>
+      </c>
+      <c r="B61" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>133.55500000000001</v>
+      </c>
+      <c r="B62" t="s">
+        <v>3</v>
+      </c>
+      <c r="C62">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="5">
+        <v>133.68100000000001</v>
+      </c>
+      <c r="B63" t="s">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="5">
+        <v>134.065</v>
+      </c>
+      <c r="B64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="5">
+        <v>134.33600000000001</v>
+      </c>
+      <c r="B65" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="5">
+        <v>134.08699999999999</v>
+      </c>
+      <c r="B66" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="5">
+        <v>134.59399999999999</v>
+      </c>
+      <c r="B67" t="s">
+        <v>8</v>
+      </c>
+      <c r="C67">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="5">
+        <v>136.00299999999999</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="5">
+        <v>136.01300000000001</v>
+      </c>
+      <c r="B69" t="s">
+        <v>10</v>
+      </c>
+      <c r="C69">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="5">
+        <v>136.08000000000001</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="5">
+        <v>136.828</v>
+      </c>
+      <c r="B71" t="s">
+        <v>12</v>
+      </c>
+      <c r="C71">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="5">
+        <v>137.42400000000001</v>
+      </c>
+      <c r="B72" t="s">
+        <v>13</v>
+      </c>
+      <c r="C72">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="5">
+        <v>137.94999999999999</v>
+      </c>
+      <c r="B73" t="s">
+        <v>14</v>
+      </c>
+      <c r="C73">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
+        <v>138.34299999999999</v>
+      </c>
+      <c r="B74" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2">
+        <v>138.726</v>
+      </c>
+      <c r="B75" t="s">
+        <v>4</v>
+      </c>
+      <c r="C75">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
+        <v>139.161</v>
+      </c>
+      <c r="B76" t="s">
+        <v>5</v>
+      </c>
+      <c r="C76">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="5">
+        <v>139.62</v>
+      </c>
+      <c r="B77" t="s">
+        <v>6</v>
+      </c>
+      <c r="C77">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="5">
+        <v>140.012</v>
+      </c>
+      <c r="B78" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="5">
+        <v>140.405</v>
+      </c>
+      <c r="B79" t="s">
+        <v>8</v>
+      </c>
+      <c r="C79">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="15">
+        <v>140.80000000000001</v>
+      </c>
+      <c r="B80" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="7">
+        <v>2025</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
